--- a/exports/securities_below_20_2026-05-19.xlsx
+++ b/exports/securities_below_20_2026-05-19.xlsx
@@ -476,22 +476,22 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>17.76</t>
+          <t>16.82</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>10,15,676</t>
+          <t>10,66,304</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>50.07</t>
+          <t>52.57</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -528,22 +528,22 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>12.52</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>9.92</t>
+          <t>9.83</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2,31,559</t>
+          <t>2,41,316</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>28.74</t>
+          <t>29.95</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -555,104 +555,104 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TPHQ</t>
+          <t>MANUGRAPH</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>13.41</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>13.84</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>13.25</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>12.93</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>13.72</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>8,11,906</t>
+          <t>4,180</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>17-Sep-2024</t>
+          <t>20-Sep-2024</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MANUGRAPH</t>
+          <t>TPHQ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>13.41</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>13.74</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>13.25</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12.93</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>13.68</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>5.80</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4,028</t>
+          <t>8,24,110</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>20-Sep-2024</t>
+          <t>17-Sep-2024</t>
         </is>
       </c>
     </row>
@@ -694,12 +694,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1,97,624</t>
+          <t>1,98,988</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>23.97</t>
+          <t>24.14</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>79,233</t>
+          <t>81,714</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>7.28</t>
+          <t>7.51</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,12 +850,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>77,379</t>
+          <t>77,479</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>7.04</t>
+          <t>7.05</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -867,203 +867,203 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>VCL</t>
+          <t>KSHITIJPOL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>3.74</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2,15,861</t>
+          <t>10,03,879</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>36.94</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>19-Sep-2024</t>
+          <t>18-Jun-2024</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SVPGLOB</t>
+          <t>KHANDSE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>18.90</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>18.90</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>17.00</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>16.97</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>17.78</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>54,633</t>
+          <t>9,349</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>20-Sep-2024</t>
+          <t>19-Sep-2024</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>KSHITIJPOL</t>
+          <t>GTLINFRA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3.74</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>9,84,215</t>
+          <t>2,33,74,375</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>36.22</t>
+          <t>306.20</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>18-Jun-2024</t>
+          <t>21-Sep-2015</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>KHANDSE</t>
+          <t>PNC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>18.90</t>
+          <t>19.10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>18.90</t>
+          <t>19.90</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>17.00</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>16.97</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>17.78</t>
+          <t>19.89</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>9,349</t>
+          <t>1,620</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1075,151 +1075,151 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GTLINFRA</t>
+          <t>SHYAMCENT</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>5.20</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2,16,90,954</t>
+          <t>89,361</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>284.15</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>21-Sep-2015</t>
+          <t>19-Sep-2024</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SHYAMCENT</t>
+          <t>FILATFASH</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>5.19</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>89,261</t>
+          <t>65,91,612</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>15.16</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>19-Sep-2024</t>
+          <t>20-Sep-2024</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FILATFASH</t>
+          <t>ROLLT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>63,39,729</t>
+          <t>2,93,109</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>14.58</t>
+          <t>6.27</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>19,18,020</t>
+          <t>19,29,630</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>32.61</t>
+          <t>32.80</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1283,156 +1283,156 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AKG</t>
+          <t>JYOTISTRUC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>12.10</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>11.70</t>
+          <t>12.69</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>12.05</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>11.06</t>
+          <t>12.10</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>11.53</t>
+          <t>12.60</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3,396</t>
+          <t>30,18,054</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>371.52</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>17-Sep-2024</t>
+          <t>10-Feb-2025</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>JYOTISTRUC</t>
+          <t>ASHOKAMET</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>12.10</t>
+          <t>15.90</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>16.60</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>12.05</t>
+          <t>15.80</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>12.10</t>
+          <t>15.66</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>12.60</t>
+          <t>16.30</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>27,52,233</t>
+          <t>9,253</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>338.25</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>10-Feb-2025</t>
+          <t>06-Sep-2024</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>HAVISHA</t>
+          <t>NEXTMEDIA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1,231</t>
+          <t>9,638</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>17-Sep-2024</t>
+          <t>22-Aug-2017</t>
         </is>
       </c>
     </row>
@@ -1474,12 +1474,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>58,20,311</t>
+          <t>58,79,196</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>30.85</t>
+          <t>31.16</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1526,12 +1526,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>5,48,479</t>
+          <t>5,60,320</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>23.53</t>
+          <t>24.04</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1,34,099</t>
+          <t>1,58,949</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>6.54</t>
+          <t>7.76</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1682,12 +1682,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>34,819</t>
+          <t>41,626</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1699,307 +1699,307 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>EUROTEXIND</t>
+          <t>ASTRON</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>15.91</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>16.09</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>15.58</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1,324</t>
+          <t>11,824</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>12-Sep-2024</t>
+          <t>23-Sep-2024</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>VIVIMEDLAB</t>
+          <t>DPSCLTD</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>6.30</t>
+          <t>9.71</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>6.50</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>6.10</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>6.32</t>
+          <t>9.94</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>9.57</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1,01,686</t>
+          <t>1,44,430</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>6.29</t>
+          <t>13.88</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>27-Dec-2024</t>
+          <t>12-Sep-2025</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DPSCLTD</t>
+          <t>EUROTEXIND</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>9.71</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>15.91</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>9.94</t>
+          <t>16.09</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>9.67</t>
+          <t>15.58</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1,42,916</t>
+          <t>1,324</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>13.73</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>12-Sep-2025</t>
+          <t>12-Sep-2024</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>RADAAN</t>
+          <t>TIJARIA</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>4.72</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>4.60</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>4.71</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>4.60</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1,249</t>
+          <t>17,358</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>23-Sep-2022</t>
+          <t>19-Sep-2024</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SEYAIND</t>
+          <t>AIRAN</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>15.05</t>
+          <t>16.27</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>15.05</t>
+          <t>16.93</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>15.05</t>
+          <t>16.25</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>15.35</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>15.05</t>
+          <t>16.29</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>4,095</t>
+          <t>16,356</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>17-Dec-2020</t>
+          <t>14-Aug-2019</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MADHUCON</t>
+          <t>AKI</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>5.70</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>5.99</t>
+          <t>4.99</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>5.60</t>
+          <t>4.70</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>4.80</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>5.60</t>
+          <t>4.70</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1,316</t>
+          <t>19,411</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2011,416 +2011,416 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>GVKPIL</t>
+          <t>SEYAIND</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>15.05</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>15.05</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>15.05</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>15.35</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>15.05</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1,75,201</t>
+          <t>4,105</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>5.40</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>27-Dec-2024</t>
+          <t>17-Dec-2020</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ALOKINDS</t>
+          <t>MADHUCON</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>13.22</t>
+          <t>5.70</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>13.29</t>
+          <t>5.99</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>12.85</t>
+          <t>5.60</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>13.18</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>12.93</t>
+          <t>5.60</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>30,71,964</t>
+          <t>1,316</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>398.74</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>20-Sep-2024</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ACCURACY</t>
+          <t>GVKPIL</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
+          <t>3.08</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>3.08</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>3.14</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>3.08</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-1.91</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>1,78,118</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
           <t>5.49</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>5.27</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>5.46</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>5.36</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>-1.83</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>74,251</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>3.94</t>
-        </is>
-      </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>15-Feb-2023</t>
+          <t>27-Dec-2024</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SUVIDHAA</t>
+          <t>RNBDENIMS</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>11.62</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>11.99</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>11.28</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>11.62</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>11.40</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>16,204</t>
+          <t>2,25,209</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>26.08</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>23-Sep-2024</t>
+          <t>02-Apr-2026</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>DISHTV</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>7.20</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>7.02</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1,697</t>
+          <t>7,38,244</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>23.11</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>23-Sep-2024</t>
+          <t>05-Nov-2018</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>GLOBE</t>
+          <t>CREATIVEYE</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>6.98</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>7.04</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>6.76</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>6.99</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>35,460</t>
+          <t>4,223</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>17-Jan-2025</t>
+          <t>23-Sep-2024</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>IBULLSLTD</t>
+          <t>SHAH</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>17.53</t>
+          <t>5.49</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>5.49</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>17.53</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>18.45</t>
+          <t>5.41</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>18.16</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>11,15,046</t>
+          <t>1,56,188</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>200.71</t>
+          <t>8.42</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>19-Sep-2024</t>
+          <t>04-May-2023</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DISHTV</t>
+          <t>ACCURACY</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>5.49</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>5.36</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>7,21,945</t>
+          <t>74,272</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>22.60</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>05-Nov-2018</t>
+          <t>15-Feb-2023</t>
         </is>
       </c>
     </row>
@@ -2452,22 +2452,22 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>13.93</t>
+          <t>13.90</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-1.70</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>11,275</t>
+          <t>11,846</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2479,42 +2479,42 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>INFOMEDIA</t>
+          <t>CINEVISTA</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>16.20</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>16.44</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>15.70</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>16.20</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>15.93</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>3,413</t>
+          <t>1,245</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2524,7 +2524,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>10-Aug-2018</t>
+          <t>13-Sep-2024</t>
         </is>
       </c>
     </row>

--- a/exports/securities_below_20_2026-05-19.xlsx
+++ b/exports/securities_below_20_2026-05-19.xlsx
@@ -476,22 +476,22 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>5.07</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>16.82</t>
+          <t>18.46</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>10,66,304</t>
+          <t>14,75,308</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>52.57</t>
+          <t>73.03</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -528,22 +528,22 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>12.52</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>9.83</t>
+          <t>9.92</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2,41,316</t>
+          <t>2,51,374</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>29.95</t>
+          <t>31.22</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -555,156 +555,156 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MANUGRAPH</t>
+          <t>TPHQ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>13.41</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>13.84</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>13.25</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>12.93</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>13.72</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4,180</t>
+          <t>8,86,510</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>20-Sep-2024</t>
+          <t>17-Sep-2024</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TPHQ</t>
+          <t>SHYAMCENT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>5.63</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>8,24,110</t>
+          <t>95,670</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>17-Sep-2024</t>
+          <t>19-Sep-2024</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HCL-INSYS</t>
+          <t>MANUGRAPH</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11.54</t>
+          <t>13.41</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>13.50</t>
+          <t>13.84</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>11.54</t>
+          <t>13.25</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>11.54</t>
+          <t>12.93</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>13.63</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.41</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1,98,988</t>
+          <t>4,430</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>24.14</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>12-Sep-2024</t>
+          <t>20-Sep-2024</t>
         </is>
       </c>
     </row>
@@ -746,12 +746,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>81,714</t>
+          <t>82,814</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>7.51</t>
+          <t>7.61</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -763,104 +763,104 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ORTINGLOBE</t>
+          <t>VIPULLTD</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>14.80</t>
+          <t>9.11</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>14.80</t>
+          <t>9.13</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>14.80</t>
+          <t>8.75</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>14.10</t>
+          <t>8.70</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>14.80</t>
+          <t>9.13</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1,678</t>
+          <t>78,454</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>22-Sep-2023</t>
+          <t>13-Sep-2024</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>VIPULLTD</t>
+          <t>SVPGLOB</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>9.11</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>9.13</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.75</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>8.70</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>9.13</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>77,479</t>
+          <t>60,834</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>7.05</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>13-Sep-2024</t>
+          <t>20-Sep-2024</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>10,03,879</t>
+          <t>12,02,886</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>36.94</t>
+          <t>44.75</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -944,17 +944,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>17.78</t>
+          <t>17.77</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>4.71</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>9,349</t>
+          <t>9,352</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -971,151 +971,151 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GTLINFRA</t>
+          <t>KESORAMIND</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>11.20</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>12.27</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>11.20</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>11.69</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>12.24</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>4.70</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2,33,74,375</t>
+          <t>10,83,090</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>306.20</t>
+          <t>129.10</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>21-Sep-2015</t>
+          <t>10-Mar-2025</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PNC</t>
+          <t>ORTINGLOBE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>19.10</t>
+          <t>14.80</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>19.90</t>
+          <t>14.80</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>14.73</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>19.01</t>
+          <t>14.10</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>19.89</t>
+          <t>14.73</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1,620</t>
+          <t>1,679</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>19-Sep-2024</t>
+          <t>22-Sep-2023</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SHYAMCENT</t>
+          <t>TIJARIA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.72</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>4.60</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.71</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>5.20</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>89,361</t>
+          <t>27,097</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1127,99 +1127,99 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FILATFASH</t>
+          <t>HYBRIDFIN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>20.08</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>18.50</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>18.79</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>19.61</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>65,91,612</t>
+          <t>888</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>15.16</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>20-Sep-2024</t>
+          <t>19-Jul-2024</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ROLLT</t>
+          <t>FILATFASH</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2,93,109</t>
+          <t>93,31,926</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>6.27</t>
+          <t>21.46</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1231,260 +1231,260 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ESSENTIA</t>
+          <t>GSS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>12.88</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>13.50</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>12.85</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>12.91</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>13.47</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>19,29,630</t>
+          <t>17,579</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>32.80</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>20-Sep-2024</t>
+          <t>23-Sep-2024</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>JYOTISTRUC</t>
+          <t>ZEEMEDIA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>12.10</t>
+          <t>7.77</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>12.05</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>12.10</t>
+          <t>7.67</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>12.60</t>
+          <t>8.00</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>30,18,054</t>
+          <t>4,11,801</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>371.52</t>
+          <t>32.53</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>10-Feb-2025</t>
+          <t>05-Oct-2017</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ASHOKAMET</t>
+          <t>ESSENTIA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>15.90</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>16.60</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>15.80</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>15.66</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>16.30</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>9,253</t>
+          <t>19,98,857</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>33.78</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>06-Sep-2024</t>
+          <t>20-Sep-2024</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>NEXTMEDIA</t>
+          <t>KELLTONTEC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>14.75</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>15.49</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>14.75</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>14.73</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>15.36</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>9,638</t>
+          <t>17,20,641</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>261.54</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>22-Aug-2017</t>
+          <t>25-Jul-2025</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>GATECH</t>
+          <t>PILITA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>7.66</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>8.43</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>7.66</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>8.03</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>8.37</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>58,79,196</t>
+          <t>7,680</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>31.16</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>28-Apr-2025</t>
+          <t>20-Jun-2024</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>5,60,320</t>
+          <t>5,99,844</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>24.04</t>
+          <t>25.73</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1,58,949</t>
+          <t>1,85,926</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>7.76</t>
+          <t>9.07</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1630,12 +1630,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>12,985</t>
+          <t>14,590</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1647,364 +1647,364 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>UMESLTD</t>
+          <t>DPSCLTD</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>4.56</t>
+          <t>9.71</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>4.56</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>9.94</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>4.56</t>
+          <t>9.51</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-4.80</t>
+          <t>-4.33</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>41,626</t>
+          <t>1,58,081</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>15.19</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>04-Sep-2024</t>
+          <t>12-Sep-2025</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ASTRON</t>
+          <t>RADAAN</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>11,824</t>
+          <t>3,444</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>23-Sep-2024</t>
+          <t>23-Sep-2022</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DPSCLTD</t>
+          <t>EUROTEXIND</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>9.71</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>15.91</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>9.94</t>
+          <t>16.09</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>9.57</t>
+          <t>15.58</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1,44,430</t>
+          <t>1,324</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>13.88</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>12-Sep-2025</t>
+          <t>12-Sep-2024</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>EUROTEXIND</t>
+          <t>RADIOCITY</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>6.32</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>15.91</t>
+          <t>6.32</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>5.95</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>16.09</t>
+          <t>6.10</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>15.58</t>
+          <t>5.95</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1,324</t>
+          <t>1,794</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>12-Sep-2024</t>
+          <t>16-Aug-2024</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>TIJARIA</t>
+          <t>SUVIDHAA</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>4.72</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>4.60</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>4.71</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>4.60</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>17,358</t>
+          <t>26,661</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>19-Sep-2024</t>
+          <t>23-Sep-2024</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AIRAN</t>
+          <t>AKSHAR</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>16.27</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>16.93</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>16.25</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>16.29</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>16,356</t>
+          <t>2,45,538</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>14-Aug-2019</t>
+          <t>20-Sep-2024</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AKI</t>
+          <t>CREATIVEYE</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>6.98</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>4.99</t>
+          <t>7.04</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>4.70</t>
+          <t>6.76</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>4.80</t>
+          <t>6.99</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>4.70</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>19,411</t>
+          <t>4,672</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>20-Sep-2024</t>
+          <t>23-Sep-2024</t>
         </is>
       </c>
     </row>
@@ -2063,468 +2063,468 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MADHUCON</t>
+          <t>GVKPIL</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>5.70</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>5.99</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>5.60</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>5.60</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1,316</t>
+          <t>2,32,956</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>7.18</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>20-Sep-2024</t>
+          <t>27-Dec-2024</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>GVKPIL</t>
+          <t>IBULLSLTD</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>17.53</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>18.75</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>17.53</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>18.45</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>18.10</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>1,78,118</t>
+          <t>14,88,991</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>268.47</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>27-Dec-2024</t>
+          <t>19-Sep-2024</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>RNBDENIMS</t>
+          <t>ALOKINDS</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>11.62</t>
+          <t>13.22</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>11.99</t>
+          <t>13.29</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>11.28</t>
+          <t>12.85</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>11.62</t>
+          <t>13.18</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>11.40</t>
+          <t>12.95</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2,25,209</t>
+          <t>37,10,256</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>26.08</t>
+          <t>481.22</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>02-Apr-2026</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DISHTV</t>
+          <t>SUPERSPIN</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>5.18</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>5.16</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>5.07</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>7,38,244</t>
+          <t>32,024</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>23.11</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>05-Nov-2018</t>
+          <t>02-Aug-2024</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CREATIVEYE</t>
+          <t>GLOBE</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>6.98</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>7.04</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>6.99</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>4,223</t>
+          <t>64,468</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>23-Sep-2024</t>
+          <t>17-Jan-2025</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SHAH</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>7.20</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>5.41</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>7.03</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>1,56,188</t>
+          <t>1,935</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>8.42</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>04-May-2023</t>
+          <t>23-Sep-2024</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ACCURACY</t>
+          <t>VIKASECO</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>5.36</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>74,272</t>
+          <t>7,31,023</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>15-Feb-2023</t>
+          <t>23-Sep-2024</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>MMWL</t>
+          <t>MAGNUM</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>14.50</t>
+          <t>20.60</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>14.63</t>
+          <t>20.60</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>13.65</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>14.14</t>
+          <t>20.10</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>13.90</t>
+          <t>19.80</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-1.70</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>11,846</t>
+          <t>1,724</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>18-Sep-2014</t>
+          <t>20-Sep-2024</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CINEVISTA</t>
+          <t>ANMOL</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>16.20</t>
+          <t>11.86</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>16.44</t>
+          <t>12.00</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>15.70</t>
+          <t>11.43</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>16.20</t>
+          <t>11.63</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>15.93</t>
+          <t>11.46</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>1,245</t>
+          <t>8,803</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>13-Sep-2024</t>
+          <t>01-Aug-2023</t>
         </is>
       </c>
     </row>

--- a/exports/securities_below_20_2026-05-19.xlsx
+++ b/exports/securities_below_20_2026-05-19.xlsx
@@ -486,12 +486,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>14,75,308</t>
+          <t>16,19,316</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>73.03</t>
+          <t>80.32</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -538,12 +538,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2,51,374</t>
+          <t>2,65,446</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>31.22</t>
+          <t>32.97</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -555,52 +555,52 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TPHQ</t>
+          <t>MANUGRAPH</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>13.41</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>13.94</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>13.25</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>12.93</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>13.94</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>7.81</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>8,86,510</t>
+          <t>10,232</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>17-Sep-2024</t>
+          <t>20-Sep-2024</t>
         </is>
       </c>
     </row>
@@ -632,22 +632,22 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>5.63</t>
+          <t>7.24</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>95,670</t>
+          <t>1,06,745</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>5.48</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -659,52 +659,52 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MANUGRAPH</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>13.41</t>
+          <t>12.98</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>13.84</t>
+          <t>13.57</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>13.25</t>
+          <t>12.86</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12.93</t>
+          <t>12.86</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>13.63</t>
+          <t>13.56</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>5.41</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4,430</t>
+          <t>96,17,04,069</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>1,27,041.11</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>20-Sep-2024</t>
+          <t>20-Aug-2024</t>
         </is>
       </c>
     </row>
@@ -746,12 +746,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>82,814</t>
+          <t>83,086</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>7.61</t>
+          <t>7.64</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -763,208 +763,208 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>VIPULLTD</t>
+          <t>ORTINGLOBE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>9.11</t>
+          <t>14.80</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>9.13</t>
+          <t>14.80</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.75</t>
+          <t>14.73</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>8.70</t>
+          <t>14.10</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>9.13</t>
+          <t>14.80</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>78,454</t>
+          <t>2,191</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>13-Sep-2024</t>
+          <t>22-Sep-2023</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SVPGLOB</t>
+          <t>VIPULLTD</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>9.11</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>9.13</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>8.75</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>8.70</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>9.13</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>60,834</t>
+          <t>78,779</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>20-Sep-2024</t>
+          <t>13-Sep-2024</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>KSHITIJPOL</t>
+          <t>SVPGLOB</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3.74</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>12,02,886</t>
+          <t>61,715</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>44.75</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>18-Jun-2024</t>
+          <t>20-Sep-2024</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>KHANDSE</t>
+          <t>KSHITIJPOL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>18.90</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>18.90</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>17.00</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>16.97</t>
+          <t>3.74</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>17.77</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>4.71</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>9,352</t>
+          <t>12,89,323</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>48.09</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>19-Sep-2024</t>
+          <t>18-Jun-2024</t>
         </is>
       </c>
     </row>
@@ -996,22 +996,22 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>12.24</t>
+          <t>12.25</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>4.70</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>10,83,090</t>
+          <t>11,34,364</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>129.10</t>
+          <t>135.33</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1023,156 +1023,156 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ORTINGLOBE</t>
+          <t>KHANDSE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>14.80</t>
+          <t>18.90</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>14.80</t>
+          <t>18.90</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>14.73</t>
+          <t>17.00</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>14.10</t>
+          <t>16.97</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>14.73</t>
+          <t>17.77</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>4.71</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1,679</t>
+          <t>9,352</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>22-Sep-2023</t>
+          <t>19-Sep-2024</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TIJARIA</t>
+          <t>ZEEMEDIA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>4.72</t>
+          <t>7.77</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>4.60</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>4.71</t>
+          <t>7.67</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>8.03</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>27,097</t>
+          <t>5,67,016</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>44.96</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>19-Sep-2024</t>
+          <t>05-Oct-2017</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>HYBRIDFIN</t>
+          <t>MADHUCON</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>5.70</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>20.08</t>
+          <t>5.99</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>18.50</t>
+          <t>5.60</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>18.79</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>19.61</t>
+          <t>5.97</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>1,869</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>19-Jul-2024</t>
+          <t>20-Sep-2024</t>
         </is>
       </c>
     </row>
@@ -1214,12 +1214,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>93,31,926</t>
+          <t>1,15,90,964</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>21.46</t>
+          <t>26.66</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1231,1300 +1231,1300 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GSS</t>
+          <t>KRIDHANINF</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12.88</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>13.50</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>12.85</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>12.91</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>13.47</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>17,579</t>
+          <t>43,046</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>23-Sep-2024</t>
+          <t>23-Sep-2022</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ZEEMEDIA</t>
+          <t>KELLTONTEC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>7.77</t>
+          <t>14.75</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>15.49</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>14.75</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>7.67</t>
+          <t>14.73</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>8.00</t>
+          <t>15.35</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>4,11,801</t>
+          <t>18,27,881</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>32.53</t>
+          <t>278.02</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>05-Oct-2017</t>
+          <t>25-Jul-2025</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ESSENTIA</t>
+          <t>GSS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>12.88</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>13.50</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>12.85</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>12.91</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>13.44</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>19,98,857</t>
+          <t>17,718</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>33.78</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>20-Sep-2024</t>
+          <t>23-Sep-2024</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>KELLTONTEC</t>
+          <t>VIVIDHA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>14.75</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>15.49</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>14.75</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>14.73</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>15.36</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>17,20,641</t>
+          <t>88,979</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>261.54</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>25-Jul-2025</t>
+          <t>14-Nov-2024</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PILITA</t>
+          <t>GATECHDVR</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>7.66</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>8.43</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>7.66</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>8.37</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>7,680</t>
+          <t>2,42,998</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>20-Jun-2024</t>
+          <t>28-Apr-2025</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>OSIAHYPER</t>
+          <t>SILLYMONKS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>16.40</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>16.40</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>14.61</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>4.51</t>
+          <t>15.80</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-5.06</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>5,99,844</t>
+          <t>18,114</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>25.73</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>12-Sep-2024</t>
+          <t>15-Feb-2021</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PARSVNATH</t>
+          <t>OSIAHYPER</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>4.51</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-4.87</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1,85,926</t>
+          <t>6,35,989</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>9.07</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>20-Sep-2024</t>
+          <t>12-Sep-2024</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>GRADIENTE</t>
+          <t>PARSVNATH</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>6.27</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>6.27</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>6.27</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>6.59</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>6.27</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-4.86</t>
+          <t>-4.87</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>14,590</t>
+          <t>2,07,262</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>10.11</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>20-Sep-2024</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DPSCLTD</t>
+          <t>GRADIENTE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>9.71</t>
+          <t>6.27</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>6.27</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>6.27</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>9.94</t>
+          <t>6.59</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>9.51</t>
+          <t>6.27</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-4.33</t>
+          <t>-4.86</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1,58,081</t>
+          <t>16,737</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>15.19</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>12-Sep-2025</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>RADAAN</t>
+          <t>DPSCLTD</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>9.71</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>9.94</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>9.50</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>3,444</t>
+          <t>1,70,905</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>16.41</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>23-Sep-2022</t>
+          <t>12-Sep-2025</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>EUROTEXIND</t>
+          <t>GTECJAINX</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>15.91</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>18.36</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>16.09</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>15.58</t>
+          <t>18.40</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1,324</t>
+          <t>1,627</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>12-Sep-2024</t>
+          <t>22-Jul-2024</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>RADIOCITY</t>
+          <t>BAIDFIN</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>6.32</t>
+          <t>10.49</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>6.32</t>
+          <t>10.84</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>5.95</t>
+          <t>9.80</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>6.10</t>
+          <t>10.49</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>5.95</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1,794</t>
+          <t>1,85,149</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>18.94</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>16-Aug-2024</t>
+          <t>17-Nov-2025</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SUVIDHAA</t>
+          <t>IBULLSLTD</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>17.53</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>18.75</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>17.53</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>18.45</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>17.90</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>26,661</t>
+          <t>17,40,994</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>313.55</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>23-Sep-2024</t>
+          <t>19-Sep-2024</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AKSHAR</t>
+          <t>EUROTEXIND</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>16.19</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>16.09</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>15.69</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2,45,538</t>
+          <t>6,500</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>20-Sep-2024</t>
+          <t>12-Sep-2024</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CREATIVEYE</t>
+          <t>SHANTI</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>6.98</t>
+          <t>6.90</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>7.04</t>
+          <t>6.90</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t>6.38</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
           <t>6.76</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>6.99</t>
-        </is>
-      </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>6.60</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>4,672</t>
+          <t>24,174</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>23-Sep-2024</t>
+          <t>20-Sep-2024</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SEYAIND</t>
+          <t>UMESLTD</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>15.05</t>
+          <t>4.56</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>15.05</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>15.05</t>
+          <t>4.56</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>15.35</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>15.05</t>
+          <t>4.68</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>4,105</t>
+          <t>45,560</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>17-Dec-2020</t>
+          <t>04-Sep-2024</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>GVKPIL</t>
+          <t>RADAAN</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2,32,956</t>
+          <t>5,723</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>7.18</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>27-Dec-2024</t>
+          <t>23-Sep-2022</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>IBULLSLTD</t>
+          <t>DUCON</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>17.53</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>17.53</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>18.45</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>18.10</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>14,88,991</t>
+          <t>1,23,461</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>268.47</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>19-Sep-2024</t>
+          <t>23-Sep-2024</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ALOKINDS</t>
+          <t>CREATIVEYE</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>13.22</t>
+          <t>6.98</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>13.29</t>
+          <t>7.04</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>12.85</t>
+          <t>6.76</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>13.18</t>
+          <t>6.99</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>12.95</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>37,10,256</t>
+          <t>5,166</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>481.22</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>23-Sep-2024</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SUPERSPIN</t>
+          <t>ALOKINDS</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>13.22</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>5.18</t>
+          <t>13.29</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>12.85</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>5.16</t>
+          <t>13.18</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>12.92</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>32,024</t>
+          <t>46,72,127</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>605.51</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>02-Aug-2024</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>GLOBE</t>
+          <t>SEYAIND</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>15.05</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>15.05</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>15.05</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>15.35</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>15.05</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>64,468</t>
+          <t>4,437</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>17-Jan-2025</t>
+          <t>17-Dec-2020</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>OSWALSEEDS</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>12.30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>7.20</t>
+          <t>12.49</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>11.91</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>12.29</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>7.03</t>
+          <t>12.05</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>1,935</t>
+          <t>50,009</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>6.05</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>23-Sep-2024</t>
+          <t>20-Sep-2024</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>VIKASECO</t>
+          <t>SUPERSPIN</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>5.18</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>5.16</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>7,31,023</t>
+          <t>34,027</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>23-Sep-2024</t>
+          <t>02-Aug-2024</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>MAGNUM</t>
+          <t>GVKPIL</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>20.60</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>20.60</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>20.10</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>19.80</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>1,724</t>
+          <t>2,70,440</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>20-Sep-2024</t>
+          <t>27-Dec-2024</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ANMOL</t>
+          <t>SUVIDHAA</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>11.86</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>12.00</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>11.43</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>11.63</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>11.46</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>8,803</t>
+          <t>33,110</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>01-Aug-2023</t>
+          <t>23-Sep-2024</t>
         </is>
       </c>
     </row>

--- a/exports/securities_below_20_2026-05-19.xlsx
+++ b/exports/securities_below_20_2026-05-19.xlsx
@@ -476,22 +476,22 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>18.46</t>
+          <t>19.86</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>16,19,316</t>
+          <t>23,10,462</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>80.32</t>
+          <t>115.75</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -538,12 +538,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2,65,446</t>
+          <t>2,88,263</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>32.97</t>
+          <t>35.83</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -555,156 +555,156 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MANUGRAPH</t>
+          <t>TECILCHEM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>13.41</t>
+          <t>11.85</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>13.94</t>
+          <t>12.45</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>13.25</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>12.93</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>13.94</t>
+          <t>12.45</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>7.81</t>
+          <t>5.87</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>10,232</t>
+          <t>779</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>20-Sep-2024</t>
+          <t>19-Sep-2024</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SHYAMCENT</t>
+          <t>SURANAT&amp;P</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>17.62</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>19.19</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>17.60</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>17.62</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>7.24</t>
+          <t>5.28</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1,06,745</t>
+          <t>1,00,407</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>18.52</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>19-Sep-2024</t>
+          <t>23-Sep-2024</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>DISHTV</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>12.98</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>13.57</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>12.86</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12.86</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>13.56</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>96,17,04,069</t>
+          <t>15,73,238</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1,27,041.11</t>
+          <t>50.34</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>20-Aug-2024</t>
+          <t>05-Nov-2018</t>
         </is>
       </c>
     </row>
@@ -746,12 +746,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>83,086</t>
+          <t>1,28,711</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>7.64</t>
+          <t>11.85</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -763,32 +763,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ORTINGLOBE</t>
+          <t>KESORAMIND</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>14.80</t>
+          <t>11.20</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>14.80</t>
+          <t>12.27</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>14.73</t>
+          <t>11.20</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>14.10</t>
+          <t>11.69</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>14.80</t>
+          <t>12.27</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -798,584 +798,584 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2,191</t>
+          <t>15,18,671</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>182.39</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>22-Sep-2023</t>
+          <t>10-Mar-2025</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>VIPULLTD</t>
+          <t>ORTINGLOBE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>9.11</t>
+          <t>14.80</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>9.13</t>
+          <t>14.80</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.75</t>
+          <t>14.73</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>8.70</t>
+          <t>14.10</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>9.13</t>
+          <t>14.80</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>78,779</t>
+          <t>2,291</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>13-Sep-2024</t>
+          <t>22-Sep-2023</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SVPGLOB</t>
+          <t>ZEEMEDIA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>7.77</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>7.67</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>61,715</t>
+          <t>6,64,972</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>52.80</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>20-Sep-2024</t>
+          <t>05-Oct-2017</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>KSHITIJPOL</t>
+          <t>BCG</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>9.15</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>9.54</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>9.12</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3.74</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>9.54</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>12,89,323</t>
+          <t>45,05,521</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>48.09</t>
+          <t>420.82</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>18-Jun-2024</t>
+          <t>23-Apr-2025</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>KESORAMIND</t>
+          <t>VIPULLTD</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>11.20</t>
+          <t>9.11</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>12.27</t>
+          <t>9.13</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>11.20</t>
+          <t>8.75</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>11.69</t>
+          <t>8.70</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>12.25</t>
+          <t>9.13</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>11,34,364</t>
+          <t>1,22,574</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>135.33</t>
+          <t>11.17</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>10-Mar-2025</t>
+          <t>13-Sep-2024</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>KHANDSE</t>
+          <t>SVPGLOB</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>18.90</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>18.90</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>17.00</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>16.97</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>17.77</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>4.71</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>9,352</t>
+          <t>74,468</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>19-Sep-2024</t>
+          <t>20-Sep-2024</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ZEEMEDIA</t>
+          <t>ARCHIES</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>7.77</t>
+          <t>14.33</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>14.99</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>14.33</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>7.67</t>
+          <t>14.26</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>5,67,016</t>
+          <t>8,330</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>44.96</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>05-Oct-2017</t>
+          <t>17-Sep-2024</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MADHUCON</t>
+          <t>KSHITIJPOL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5.70</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>5.99</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>5.60</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>3.74</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>5.97</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1,869</t>
+          <t>15,83,456</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>59.70</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>20-Sep-2024</t>
+          <t>18-Jun-2024</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FILATFASH</t>
+          <t>KRIDHANINF</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>4.68</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1,15,90,964</t>
+          <t>52,917</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>26.66</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>20-Sep-2024</t>
+          <t>23-Sep-2022</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>KRIDHANINF</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>12.98</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>13.68</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>12.86</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>12.86</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>13.45</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>43,046</t>
+          <t>1,54,34,30,179</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>2,05,893.59</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>23-Sep-2022</t>
+          <t>20-Aug-2024</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>KELLTONTEC</t>
+          <t>INFOMEDIA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>14.75</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>15.49</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>14.75</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>14.73</t>
+          <t>5.69</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>15.35</t>
+          <t>5.95</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>18,27,881</t>
+          <t>9,997</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>278.02</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>25-Jul-2025</t>
+          <t>10-Aug-2018</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GSS</t>
+          <t>RANASUG</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>12.30</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
           <t>12.88</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>13.50</t>
-        </is>
-      </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>12.85</t>
+          <t>12.30</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>12.91</t>
+          <t>12.32</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>13.44</t>
+          <t>12.87</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>17,718</t>
+          <t>2,25,800</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>28.50</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1387,572 +1387,572 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>VIVIDHA</t>
+          <t>MKPL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>5.05</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>88,979</t>
+          <t>3,29,078</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>16.78</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>14-Nov-2024</t>
+          <t>23-Sep-2024</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>GATECHDVR</t>
+          <t>FILATFASH</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2,42,998</t>
+          <t>2,79,19,929</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>64.22</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>28-Apr-2025</t>
+          <t>20-Sep-2024</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SILLYMONKS</t>
+          <t>DPSCLTD</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>16.40</t>
+          <t>9.71</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>16.40</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>14.61</t>
+          <t>9.30</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>15.80</t>
+          <t>9.94</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>9.36</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-5.06</t>
+          <t>-5.84</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>18,114</t>
+          <t>3,07,379</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>29.26</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>15-Feb-2021</t>
+          <t>12-Sep-2025</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>OSIAHYPER</t>
+          <t>IBULLSLTD</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>17.53</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>18.75</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>17.53</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>4.51</t>
+          <t>18.45</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>17.53</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-4.99</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6,35,989</t>
+          <t>53,30,533</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>27.28</t>
+          <t>946.17</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>12-Sep-2024</t>
+          <t>19-Sep-2024</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PARSVNATH</t>
+          <t>OSIAHYPER</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>4.51</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-4.87</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2,07,262</t>
+          <t>8,28,829</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>10.11</t>
+          <t>35.56</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>20-Sep-2024</t>
+          <t>12-Sep-2024</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>GRADIENTE</t>
+          <t>PARSVNATH</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>6.27</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>6.27</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>6.27</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>6.59</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>6.27</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-4.86</t>
+          <t>-4.87</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>16,737</t>
+          <t>3,17,539</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>15.50</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>20-Sep-2024</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DPSCLTD</t>
+          <t>GRADIENTE</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>9.71</t>
+          <t>6.27</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>6.27</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>6.27</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>9.94</t>
+          <t>6.59</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>9.50</t>
+          <t>6.27</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-4.86</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1,70,905</t>
+          <t>38,259</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>16.41</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>12-Sep-2025</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>GTECJAINX</t>
+          <t>SILLYMONKS</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>16.40</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>16.40</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>18.36</t>
+          <t>14.61</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>15.80</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>18.40</t>
+          <t>15.10</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1,627</t>
+          <t>37,657</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>22-Jul-2024</t>
+          <t>15-Feb-2021</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BAIDFIN</t>
+          <t>SPCENET</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>10.49</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>10.84</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>9.80</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>10.49</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1,85,149</t>
+          <t>6,44,333</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>18.94</t>
+          <t>23.20</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>17-Nov-2025</t>
+          <t>20-Sep-2024</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>IBULLSLTD</t>
+          <t>EASEMYTRIP</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>17.53</t>
+          <t>8.24</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>8.31</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>17.53</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>18.45</t>
+          <t>8.23</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>17.90</t>
+          <t>7.97</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>17,40,994</t>
+          <t>1,77,26,014</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>313.55</t>
+          <t>1,441.12</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>19-Sep-2024</t>
+          <t>29-Nov-2024</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>EUROTEXIND</t>
+          <t>SHAH</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>5.49</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>16.19</t>
+          <t>5.49</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>16.09</t>
+          <t>5.41</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>15.69</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6,500</t>
+          <t>17,80,655</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>94.02</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>12-Sep-2024</t>
+          <t>04-May-2023</t>
         </is>
       </c>
     </row>
@@ -1984,22 +1984,22 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>6.60</t>
+          <t>6.55</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-3.11</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>24,174</t>
+          <t>37,473</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2011,468 +2011,468 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>UMESLTD</t>
+          <t>RAJMET</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>4.56</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>4.56</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>45,560</t>
+          <t>7,20,666</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>27.67</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>04-Sep-2024</t>
+          <t>19-Sep-2024</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>RADAAN</t>
+          <t>MAGNUM</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>20.60</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>20.60</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>19.51</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>20.10</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>19.51</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>5,723</t>
+          <t>12,880</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>23-Sep-2022</t>
+          <t>20-Sep-2024</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>DUCON</t>
+          <t>ASHIMASYN</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>16.35</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>16.97</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>16.10</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>16.59</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>16.12</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>1,23,461</t>
+          <t>59,372</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>9.79</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>23-Sep-2024</t>
+          <t>11-Aug-2022</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CREATIVEYE</t>
+          <t>CINEVISTA</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>6.98</t>
+          <t>16.20</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>7.04</t>
+          <t>16.44</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>15.69</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>6.99</t>
+          <t>16.20</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>15.78</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>5,166</t>
+          <t>6,550</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>23-Sep-2024</t>
+          <t>13-Sep-2024</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ALOKINDS</t>
+          <t>AVROIND</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>13.22</t>
+          <t>10.70</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>13.29</t>
+          <t>10.70</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>12.85</t>
+          <t>10.02</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>13.18</t>
+          <t>10.42</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>12.92</t>
+          <t>10.16</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>46,72,127</t>
+          <t>1,02,682</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>605.51</t>
+          <t>10.57</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>05-May-2026</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SEYAIND</t>
+          <t>ALOKINDS</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>15.05</t>
+          <t>13.22</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>15.05</t>
+          <t>13.29</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>15.05</t>
+          <t>12.83</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>15.35</t>
+          <t>13.18</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>15.05</t>
+          <t>12.85</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>4,437</t>
+          <t>82,58,868</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>1,067.87</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>17-Dec-2020</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>OSWALSEEDS</t>
+          <t>TREEHOUSE</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>12.30</t>
+          <t>7.61</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>12.49</t>
+          <t>7.61</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>11.91</t>
+          <t>7.13</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>12.29</t>
+          <t>7.34</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>12.05</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>50,009</t>
+          <t>33,837</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>20-Sep-2024</t>
+          <t>05-Sep-2024</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SUPERSPIN</t>
+          <t>DELPHIFX</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>11.37</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>5.18</t>
+          <t>11.75</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>11.30</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>5.16</t>
+          <t>11.58</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>11.30</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>34,027</t>
+          <t>47,951</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>5.51</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>02-Aug-2024</t>
+          <t>13-Feb-2026</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>GVKPIL</t>
+          <t>ROLLT</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-2.40</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2,70,440</t>
+          <t>6,36,946</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>13.50</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>27-Dec-2024</t>
+          <t>20-Sep-2024</t>
         </is>
       </c>
     </row>
@@ -2504,22 +2504,22 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>33,110</t>
+          <t>75,903</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
